--- a/data/trans_orig/IP07C05-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07C05-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  triste en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de sentirse triste en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10886</t>
+          <t>10747</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10791</t>
+          <t>11072</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18854</t>
+          <t>18559</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9602</t>
+          <t>9770</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20312</t>
+          <t>20169</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>10295</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21459</t>
+          <t>21628</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>22178</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>37680</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,03%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30113</t>
+          <t>30293</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41474</t>
+          <t>41588</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38946</t>
+          <t>39145</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51013</t>
+          <t>51644</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>72692</t>
+          <t>71646</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>90398</t>
+          <t>89574</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,39%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4169</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>534</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>6773</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14066</t>
+          <t>13588</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11580</t>
+          <t>12246</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>11224</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22904</t>
+          <t>23111</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20095</t>
+          <t>19434</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33286</t>
+          <t>33474</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21220</t>
+          <t>21625</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34594</t>
+          <t>35693</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43908</t>
+          <t>44092</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63330</t>
+          <t>62522</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53034</t>
+          <t>52902</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67778</t>
+          <t>68117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48634</t>
+          <t>47794</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62828</t>
+          <t>62785</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>105822</t>
+          <t>106601</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>127253</t>
+          <t>126889</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,34%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>4530</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3540</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10533</t>
+          <t>10788</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>11397</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18809</t>
+          <t>18710</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14975</t>
+          <t>14797</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26056</t>
+          <t>25707</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>9921</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20836</t>
+          <t>20494</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28297</t>
+          <t>28821</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43636</t>
+          <t>43966</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,96%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21152</t>
+          <t>21475</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32197</t>
+          <t>32757</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32289</t>
+          <t>32103</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43644</t>
+          <t>43472</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>56149</t>
+          <t>57012</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72893</t>
+          <t>73172</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,17%</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>11489</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24352</t>
+          <t>23498</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16518</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20317</t>
+          <t>19508</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>36717</t>
+          <t>36043</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21383</t>
+          <t>21574</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22139</t>
+          <t>21967</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21890</t>
+          <t>22077</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>39253</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35610</t>
+          <t>35554</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50496</t>
+          <t>50683</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>53324</t>
+          <t>53390</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67511</t>
+          <t>67734</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>92667</t>
+          <t>94271</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>114130</t>
+          <t>113612</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,86%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>592</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8530</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2590</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9892</t>
+          <t>9736</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>488</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11547</t>
+          <t>12565</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>30262</t>
+          <t>30828</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>49014</t>
+          <t>49216</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>23304</t>
+          <t>23296</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>39896</t>
+          <t>40169</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>58101</t>
+          <t>56219</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>82982</t>
+          <t>82463</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>63627</t>
+          <t>64658</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>88073</t>
+          <t>88139</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>62703</t>
+          <t>63137</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>87159</t>
+          <t>87848</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>132883</t>
+          <t>133695</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>168515</t>
+          <t>168752</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>154087</t>
+          <t>154549</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>180241</t>
+          <t>180259</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>186682</t>
+          <t>186257</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>213346</t>
+          <t>212644</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>348536</t>
+          <t>348355</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>385780</t>
+          <t>385785</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  triste en 2012 (tasa de respuesta: 95,72%)</t>
+          <t>Menores según la frecuencia de sentirse triste en 2012 (tasa de respuesta: 95,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4523,47 +4523,47 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5717</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>7,94%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2158</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5944</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>2158</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16753</t>
+          <t>16621</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18645</t>
+          <t>17722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15960</t>
+          <t>15615</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30713</t>
+          <t>31386</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15218</t>
+          <t>15324</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28318</t>
+          <t>28261</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>19389</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32703</t>
+          <t>33499</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38825</t>
+          <t>38087</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56411</t>
+          <t>56937</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>42,04%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24011</t>
+          <t>24295</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37593</t>
+          <t>37954</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24862</t>
+          <t>25574</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38913</t>
+          <t>39383</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>52903</t>
+          <t>53791</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72771</t>
+          <t>74018</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>54,66%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6841</t>
+          <t>6871</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13910</t>
+          <t>14165</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26575</t>
+          <t>26591</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13586</t>
+          <t>13590</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26085</t>
+          <t>25489</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30277</t>
+          <t>29843</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47597</t>
+          <t>47481</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22537</t>
+          <t>22377</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36024</t>
+          <t>36621</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22149</t>
+          <t>22154</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36212</t>
+          <t>36281</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48511</t>
+          <t>48769</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68099</t>
+          <t>69986</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>36,26%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36831</t>
+          <t>36392</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52164</t>
+          <t>52227</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38981</t>
+          <t>38551</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53856</t>
+          <t>54264</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>80391</t>
+          <t>80149</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>102034</t>
+          <t>101981</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,84%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>8078</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>982</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15753</t>
+          <t>15405</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11298</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21833</t>
+          <t>22001</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>18623</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>33781</t>
+          <t>34421</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18696</t>
+          <t>19053</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31123</t>
+          <t>31870</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13537</t>
+          <t>13780</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25636</t>
+          <t>25089</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36327</t>
+          <t>35201</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53069</t>
+          <t>52772</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,31%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19134</t>
+          <t>20087</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31788</t>
+          <t>32054</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24717</t>
+          <t>25127</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37605</t>
+          <t>37590</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48123</t>
+          <t>48689</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>66060</t>
+          <t>66525</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,55%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>761</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>6981</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1555</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>718</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4636</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8331</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14256</t>
+          <t>14669</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27964</t>
+          <t>28056</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12136</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25918</t>
+          <t>25161</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>29733</t>
+          <t>30299</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>48816</t>
+          <t>48961</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15850</t>
+          <t>15783</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30711</t>
+          <t>29917</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20649</t>
+          <t>20216</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35715</t>
+          <t>35451</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40121</t>
+          <t>39544</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61247</t>
+          <t>59768</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>28863</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44802</t>
+          <t>45631</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33551</t>
+          <t>33879</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48924</t>
+          <t>49504</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>67585</t>
+          <t>67260</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>90704</t>
+          <t>90188</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,37%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13110</t>
+          <t>12860</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7606</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>16646</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>3908</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12417</t>
+          <t>13045</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17877</t>
+          <t>18753</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>50587</t>
+          <t>49945</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>74691</t>
+          <t>73421</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>53156</t>
+          <t>53936</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>76048</t>
+          <t>78356</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>110361</t>
+          <t>109637</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>143981</t>
+          <t>146016</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>84006</t>
+          <t>85220</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>111273</t>
+          <t>112037</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>86767</t>
+          <t>88411</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>114854</t>
+          <t>115306</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>180477</t>
+          <t>177593</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>219074</t>
+          <t>219497</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>124094</t>
+          <t>124169</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>153226</t>
+          <t>151750</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>137260</t>
+          <t>137110</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>166767</t>
+          <t>165951</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>270628</t>
+          <t>269591</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>311839</t>
+          <t>311060</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  triste en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de sentirse triste en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>759</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>18366</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13190</t>
+          <t>14042</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13097</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27823</t>
+          <t>28384</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,27%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13964</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27557</t>
+          <t>26487</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>18703</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32878</t>
+          <t>32799</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37157</t>
+          <t>36276</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55018</t>
+          <t>56443</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>40,3%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26352</t>
+          <t>26729</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40562</t>
+          <t>40668</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29522</t>
+          <t>29903</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43745</t>
+          <t>44504</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60001</t>
+          <t>60456</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>80255</t>
+          <t>81410</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>58,13%</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2846</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1734</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4777</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2387</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9188</t>
+          <t>9173</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>12130</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24156</t>
+          <t>24368</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11528</t>
+          <t>11798</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23414</t>
+          <t>24188</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26067</t>
+          <t>25904</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44270</t>
+          <t>43217</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27896</t>
+          <t>28193</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42707</t>
+          <t>43560</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26707</t>
+          <t>27129</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42109</t>
+          <t>42777</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59623</t>
+          <t>59269</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80505</t>
+          <t>80342</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,83%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38079</t>
+          <t>37943</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54199</t>
+          <t>54066</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43191</t>
+          <t>42026</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59298</t>
+          <t>58443</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85314</t>
+          <t>86235</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>108148</t>
+          <t>110195</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>53,26%</t>
         </is>
       </c>
     </row>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>523</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9569,7 +9569,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>7515</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13368</t>
+          <t>13717</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13907</t>
+          <t>13436</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27526</t>
+          <t>27907</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17459</t>
+          <t>17048</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30341</t>
+          <t>29476</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14394</t>
+          <t>13863</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26992</t>
+          <t>26964</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34349</t>
+          <t>34807</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>52828</t>
+          <t>52629</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,41%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26542</t>
+          <t>26557</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39647</t>
+          <t>39510</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38054</t>
+          <t>38429</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52391</t>
+          <t>53271</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68715</t>
+          <t>69135</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88912</t>
+          <t>89673</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>62,04%</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>561</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11127</t>
+          <t>11273</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24629</t>
+          <t>23775</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18627</t>
+          <t>18833</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20444</t>
+          <t>20732</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>37591</t>
+          <t>37408</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27287</t>
+          <t>26864</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43432</t>
+          <t>43393</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32273</t>
+          <t>31628</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47864</t>
+          <t>47502</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>63416</t>
+          <t>63656</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>85923</t>
+          <t>86883</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42831</t>
+          <t>42042</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59784</t>
+          <t>59526</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>38522</t>
+          <t>38173</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>54721</t>
+          <t>54829</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>86105</t>
+          <t>85688</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>110297</t>
+          <t>109547</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>53,86%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>520</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>13768</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18673</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>46844</t>
+          <t>47664</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>71346</t>
+          <t>71415</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>35457</t>
+          <t>35791</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>56786</t>
+          <t>56614</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>87486</t>
+          <t>87960</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>118492</t>
+          <t>118842</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>99111</t>
+          <t>100142</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>128520</t>
+          <t>128006</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>104216</t>
+          <t>105434</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>134083</t>
+          <t>134358</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>213321</t>
+          <t>212435</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>255414</t>
+          <t>255096</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,71%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>148101</t>
+          <t>148667</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>179895</t>
+          <t>179183</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>163112</t>
+          <t>163627</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>195184</t>
+          <t>194537</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>321411</t>
+          <t>321812</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>365290</t>
+          <t>365179</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,55%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  triste en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de sentirse triste en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -11812,7 +11812,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>7392</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15553</t>
+          <t>15934</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22335</t>
+          <t>23362</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16603</t>
+          <t>17161</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35609</t>
+          <t>35997</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,45%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12649</t>
+          <t>12744</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21958</t>
+          <t>21820</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22540</t>
+          <t>21384</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39241</t>
+          <t>40199</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37781</t>
+          <t>37764</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>58807</t>
+          <t>60280</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>76,12%</t>
         </is>
       </c>
     </row>
@@ -12346,7 +12346,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>378</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12529,7 +12529,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2288</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9814</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30701</t>
+          <t>32081</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13230</t>
+          <t>12869</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36447</t>
+          <t>36858</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13405</t>
+          <t>14168</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25406</t>
+          <t>26413</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25508</t>
+          <t>24853</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44038</t>
+          <t>43804</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43260</t>
+          <t>42074</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65364</t>
+          <t>65171</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,67%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20498</t>
+          <t>20578</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32960</t>
+          <t>32457</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40127</t>
+          <t>40063</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61159</t>
+          <t>60842</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>64792</t>
+          <t>63941</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>89727</t>
+          <t>89162</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,01%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13006</t>
+          <t>13490</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22314</t>
+          <t>22192</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8190</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>32326</t>
+          <t>31526</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18629</t>
+          <t>18042</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17415</t>
+          <t>17033</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>10251</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29617</t>
+          <t>30587</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>43448</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67145</t>
+          <t>66882</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34091</t>
+          <t>34228</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52362</t>
+          <t>52017</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>84691</t>
+          <t>84383</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>118669</t>
+          <t>118574</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,45%</t>
         </is>
       </c>
     </row>
@@ -13710,7 +13710,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>840</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8655</t>
+          <t>8428</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>762</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>12670</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17343</t>
+          <t>18078</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11320</t>
+          <t>11503</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25422</t>
+          <t>26024</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16356</t>
+          <t>16452</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28613</t>
+          <t>28688</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10747</t>
+          <t>10854</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23216</t>
+          <t>23060</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30385</t>
+          <t>31210</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>48143</t>
+          <t>49406</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>44,97%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16471</t>
+          <t>16477</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28823</t>
+          <t>28908</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18774</t>
+          <t>17687</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>32283</t>
+          <t>31302</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38962</t>
+          <t>38558</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>56558</t>
+          <t>56499</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,43%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>12423</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -14505,7 +14505,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14520,7 +14520,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2312</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12202</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>12354</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>28951</t>
+          <t>28186</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>27413</t>
+          <t>27327</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>57540</t>
+          <t>59010</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>43564</t>
+          <t>42691</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>78920</t>
+          <t>80971</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>39723</t>
+          <t>38866</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>78182</t>
+          <t>77187</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>60667</t>
+          <t>60757</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>91262</t>
+          <t>91568</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>111479</t>
+          <t>112537</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>160231</t>
+          <t>160536</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>103589</t>
+          <t>105315</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>155894</t>
+          <t>157684</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>132144</t>
+          <t>131434</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>170443</t>
+          <t>170829</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>246457</t>
+          <t>245352</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>310916</t>
+          <t>313463</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,95%</t>
         </is>
       </c>
     </row>
